--- a/RESULTS/result_370FL_15A_without_prep.xlsx
+++ b/RESULTS/result_370FL_15A_without_prep.xlsx
@@ -60,7 +60,7 @@
     <t>Nbr_sts_used</t>
   </si>
   <si>
-    <t>370FL_15A_2</t>
+    <t>370FL_15A_1</t>
   </si>
 </sst>
 </file>
@@ -470,19 +470,19 @@
         <v>0.0</v>
       </c>
       <c r="G2">
-        <v>18158</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>47.1398</v>
+        <v>0.0537</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1.0</v>
+        <v>-0.0</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
